--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>8.719181529231212</v>
+        <v>8.897545086625456</v>
       </c>
       <c r="D2" t="n">
-        <v>4.480730118115394</v>
+        <v>4.485325260506302</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>9.173093261087702</v>
+        <v>9.010265339480664</v>
       </c>
       <c r="G2" t="n">
-        <v>1.273760754719416</v>
+        <v>1.128339828729399</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J2" t="n">
-        <v>0.681807293715555</v>
+        <v>0.9669675880680698</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,31 +540,31 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>5.106147662392193</v>
+        <v>5.193308482197169</v>
       </c>
       <c r="D3" t="n">
-        <v>3.165739374241148</v>
+        <v>3.201493398498276</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>13.17523134982114</v>
+        <v>12.8186803675213</v>
       </c>
       <c r="G3" t="n">
-        <v>2.956186527784157</v>
+        <v>2.66909019341811</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
         <v>14</v>
       </c>
       <c r="J3" t="n">
-        <v>3.900980155739656e-07</v>
+        <v>9.564223120529435e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.170294046721897e-05</v>
+        <v>2.86926693615883e-05</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -568,31 +580,31 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>7.827260455474121</v>
+        <v>7.865988220045442</v>
       </c>
       <c r="D4" t="n">
-        <v>3.325953406206339</v>
+        <v>3.389009489371327</v>
       </c>
       <c r="E4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>11.93521014870147</v>
+        <v>11.84338298288829</v>
       </c>
       <c r="G4" t="n">
-        <v>3.013658721728258</v>
+        <v>3.083249047556417</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003338842872497149</v>
+        <v>0.0007954948428106371</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01001652861749145</v>
+        <v>0.02386484528431911</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>7.709188007411459</v>
+        <v>7.504374299579365</v>
       </c>
       <c r="D5" t="n">
-        <v>3.229587643402907</v>
+        <v>3.133067690718373</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>16.68856045450076</v>
+        <v>16.7261387797556</v>
       </c>
       <c r="G5" t="n">
-        <v>1.164587249304075</v>
+        <v>1.190388049577508</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,31 +660,31 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>9.745389129409835</v>
+        <v>10.09129300734604</v>
       </c>
       <c r="D6" t="n">
-        <v>4.351317677254406</v>
+        <v>4.090433160369882</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>13.43985450705909</v>
+        <v>13.61033806699069</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18107376299529</v>
+        <v>2.135486239849116</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0034864458212706</v>
+        <v>0.005075540158859864</v>
       </c>
       <c r="K6" t="n">
-        <v>0.104593374638118</v>
+        <v>0.1522662047657959</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -688,31 +700,31 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>5.51984010493579</v>
+        <v>5.413936188043789</v>
       </c>
       <c r="D7" t="n">
-        <v>3.234046898234098</v>
+        <v>3.257984421205329</v>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>9.963271532299601</v>
+        <v>9.901058398760043</v>
       </c>
       <c r="G7" t="n">
-        <v>1.392398664010892</v>
+        <v>1.412143533522264</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>2.356666862382452e-05</v>
+        <v>4.657865901112364e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007070000587147356</v>
+        <v>0.001397359770333709</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -728,31 +740,31 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>7.136068384495473</v>
+        <v>7.375771299151655</v>
       </c>
       <c r="D8" t="n">
-        <v>2.762703241610127</v>
+        <v>2.552276252462985</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>13.25632450878598</v>
+        <v>13.1532702037965</v>
       </c>
       <c r="G8" t="n">
-        <v>2.269692765118377</v>
+        <v>2.300637107373936</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
         <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>3.900980155739656e-07</v>
+        <v>9.564223120529435e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.170294046721897e-05</v>
+        <v>2.86926693615883e-05</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -768,31 +780,31 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>8.09581156176548</v>
+        <v>8.457495813746519</v>
       </c>
       <c r="D9" t="n">
-        <v>5.356504931028161</v>
+        <v>5.159192152623373</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>14.15179468921388</v>
+        <v>14.13069888852507</v>
       </c>
       <c r="G9" t="n">
-        <v>2.005290621396007</v>
+        <v>2.06517537350004</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
         <v>54</v>
       </c>
       <c r="J9" t="n">
-        <v>5.149589820808515e-05</v>
+        <v>0.0001469998802153171</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001544876946242555</v>
+        <v>0.004409996406459514</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -808,31 +820,31 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>8.400163788601672</v>
+        <v>8.604605938572792</v>
       </c>
       <c r="D10" t="n">
-        <v>3.689235697059092</v>
+        <v>3.623899517442554</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>14.39620710388255</v>
+        <v>14.1906416483323</v>
       </c>
       <c r="G10" t="n">
-        <v>2.158778033125266</v>
+        <v>2.057479306775243</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
         <v>37</v>
       </c>
       <c r="J10" t="n">
-        <v>7.313484223787676e-06</v>
+        <v>1.995285603988161e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0002194045267136303</v>
+        <v>0.0005985856811964483</v>
       </c>
       <c r="L10" t="b">
         <v>1</v>
@@ -848,31 +860,31 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>8.654018247619392</v>
+        <v>8.56397965314428</v>
       </c>
       <c r="D11" t="n">
-        <v>2.77348277779855</v>
+        <v>2.794645168827317</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>14.33726006377876</v>
+        <v>14.20910101275283</v>
       </c>
       <c r="G11" t="n">
-        <v>3.57745107071537</v>
+        <v>3.649495897169222</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001653148724794089</v>
+        <v>0.0002829423989985731</v>
       </c>
       <c r="K11" t="n">
-        <v>0.004959446174382267</v>
+        <v>0.008488271969957193</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>7.930220746226476</v>
+        <v>8.192773686033528</v>
       </c>
       <c r="D12" t="n">
-        <v>3.795035273394186</v>
+        <v>3.644041314466083</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
-        <v>16.21236473313704</v>
+        <v>16.08460921040304</v>
       </c>
       <c r="G12" t="n">
-        <v>1.784821595905772</v>
+        <v>1.762731498633222</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>7.398027950986396e-08</v>
+        <v>1.679640427507783e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>2.219408385295919e-06</v>
+        <v>5.03892128252335e-06</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>11.92861757336942</v>
+        <v>12.06786501052388</v>
       </c>
       <c r="D13" t="n">
-        <v>3.290874676367733</v>
+        <v>3.285780565155649</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>11.34364842042308</v>
+        <v>11.53146247777953</v>
       </c>
       <c r="G13" t="n">
-        <v>2.066982878441712</v>
+        <v>1.984888993398642</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4269792229942408</v>
+        <v>0.4477229127520573</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,31 +980,31 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>7.459598551647202</v>
+        <v>7.626426710367629</v>
       </c>
       <c r="D14" t="n">
-        <v>2.813875829794846</v>
+        <v>2.748093649183331</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>11.94304355651317</v>
+        <v>11.5348112585766</v>
       </c>
       <c r="G14" t="n">
-        <v>4.720382609601429</v>
+        <v>4.565252060456912</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
         <v>122</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02109724366913392</v>
+        <v>0.05501626331029618</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6329173100740177</v>
+        <v>1</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
@@ -1008,31 +1020,31 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>11.57498581081627</v>
+        <v>11.59014519527221</v>
       </c>
       <c r="D15" t="n">
-        <v>2.217710328415072</v>
+        <v>2.262171646124603</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>14.10290173171374</v>
+        <v>14.27128290919227</v>
       </c>
       <c r="G15" t="n">
-        <v>1.824001125919216</v>
+        <v>1.747263176590823</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0004921657315485382</v>
+        <v>0.0002829423989985731</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01476497194645615</v>
+        <v>0.008488271969957193</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1048,31 +1060,31 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.388384047871813</v>
+        <v>8.484228878108405</v>
       </c>
       <c r="D16" t="n">
-        <v>2.955906918397099</v>
+        <v>2.978554626169707</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>11.81246074002803</v>
+        <v>11.85010757007291</v>
       </c>
       <c r="G16" t="n">
-        <v>1.467869136181002</v>
+        <v>1.505061780692417</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0001491484485850014</v>
+        <v>0.0002829423989985731</v>
       </c>
       <c r="K16" t="n">
-        <v>0.004474453457550041</v>
+        <v>0.008488271969957193</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -1088,34 +1100,34 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>10.60587100230147</v>
+        <v>10.54388363104155</v>
       </c>
       <c r="D17" t="n">
-        <v>3.254064164326222</v>
+        <v>3.306671785454962</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>14.55471214546154</v>
+        <v>14.49092901014727</v>
       </c>
       <c r="G17" t="n">
-        <v>3.081686949374003</v>
+        <v>3.165625247143857</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001485579758789372</v>
+        <v>0.002502301221356914</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04456739276368115</v>
+        <v>0.07506903664070742</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1128,31 +1140,31 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>7.89205983263593</v>
+        <v>8.013718545254294</v>
       </c>
       <c r="D18" t="n">
-        <v>4.727433351038751</v>
+        <v>4.786418053545113</v>
       </c>
       <c r="E18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
-        <v>13.43140038111322</v>
+        <v>13.23058687397816</v>
       </c>
       <c r="G18" t="n">
-        <v>3.278383166590922</v>
+        <v>3.276276903691044</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0001344791046945485</v>
+        <v>0.0003147731734286287</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004034373140836455</v>
+        <v>0.00944319520285886</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -1168,31 +1180,31 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.30638261546045</v>
+        <v>9.634609321043735</v>
       </c>
       <c r="D19" t="n">
-        <v>4.426457960747663</v>
+        <v>4.209110108848351</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>12.80779248420551</v>
+        <v>12.47066847107585</v>
       </c>
       <c r="G19" t="n">
-        <v>3.307311875040023</v>
+        <v>3.112854337230971</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
         <v>116</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01389412783410526</v>
+        <v>0.03712424730404878</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4168238350231577</v>
+        <v>1</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>9.634059263144671</v>
+        <v>9.547374377280294</v>
       </c>
       <c r="D20" t="n">
-        <v>3.048852799342233</v>
+        <v>3.081389183056837</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>15.23601013450607</v>
+        <v>15.1236467306409</v>
       </c>
       <c r="G20" t="n">
-        <v>1.83275768612754</v>
+        <v>1.831475960826261</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
-        <v>5.827356516384304e-07</v>
+        <v>1.100325600531724e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>1.748206954915291e-05</v>
+        <v>3.300976801595173e-05</v>
       </c>
       <c r="L20" t="b">
         <v>1</v>
@@ -1248,31 +1260,31 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>8.919758267174323</v>
+        <v>9.241230614300591</v>
       </c>
       <c r="D21" t="n">
-        <v>3.627239893223568</v>
+        <v>3.334885362189446</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>12.87495922345479</v>
+        <v>12.95533601923508</v>
       </c>
       <c r="G21" t="n">
-        <v>2.281607168642407</v>
+        <v>2.328360405607785</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0004058747458892882</v>
+        <v>0.0007954948428106371</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01217624237667865</v>
+        <v>0.02386484528431911</v>
       </c>
       <c r="L21" t="b">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>7.276140861240683</v>
+        <v>7.152504241643578</v>
       </c>
       <c r="D22" t="n">
-        <v>2.85214297361247</v>
+        <v>2.844558989873878</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
-        <v>16.69847968540177</v>
+        <v>16.79655825340718</v>
       </c>
       <c r="G22" t="n">
-        <v>3.320172567517286</v>
+        <v>3.398380143824604</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
         <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.13074397866807e-07</v>
+        <v>2.620605590347779e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>3.392231936004209e-06</v>
+        <v>7.861816771043338e-06</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>6.387682182091081</v>
+        <v>6.408370467175241</v>
       </c>
       <c r="D23" t="n">
-        <v>3.139775069020982</v>
+        <v>3.202849538674564</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>11.33009578260694</v>
+        <v>11.11894820566535</v>
       </c>
       <c r="G23" t="n">
-        <v>2.10194654149685</v>
+        <v>1.984036133755225</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
         <v>44</v>
       </c>
       <c r="J23" t="n">
-        <v>1.670002705729528e-05</v>
+        <v>4.657865901112364e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0005010008117188584</v>
+        <v>0.001397359770333709</v>
       </c>
       <c r="L23" t="b">
         <v>1</v>
@@ -1368,31 +1380,31 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>12.95241899218375</v>
+        <v>13.23358730525087</v>
       </c>
       <c r="D24" t="n">
-        <v>2.859401008363385</v>
+        <v>2.557431825434875</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
-        <v>17.0291345592092</v>
+        <v>17.02452779320458</v>
       </c>
       <c r="G24" t="n">
-        <v>1.380308195118864</v>
+        <v>1.422662329621984</v>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
-        <v>1.323214327606178e-05</v>
+        <v>2.551425383401997e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0003969642982818533</v>
+        <v>0.000765427615020599</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1408,31 +1420,31 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.481218316655065</v>
+        <v>9.485677937240881</v>
       </c>
       <c r="D25" t="n">
-        <v>3.696154701418407</v>
+        <v>3.772306193889517</v>
       </c>
       <c r="E25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>12.83886758714168</v>
+        <v>12.78158495334409</v>
       </c>
       <c r="G25" t="n">
-        <v>2.816162310265283</v>
+        <v>2.893209496446326</v>
       </c>
       <c r="H25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004821294618641873</v>
+        <v>0.008375319316666029</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1446388385592562</v>
+        <v>0.2512595794999809</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>11.25588969774635</v>
+        <v>11.27284520944722</v>
       </c>
       <c r="D26" t="n">
-        <v>2.400871436327574</v>
+        <v>2.448912154050222</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>16.07266762615545</v>
+        <v>15.93584317004917</v>
       </c>
       <c r="G26" t="n">
-        <v>1.981898263159543</v>
+        <v>1.963456118799252</v>
       </c>
       <c r="H26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
         <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>2.596517460604548e-07</v>
+        <v>6.25339355892696e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>7.789552381813643e-06</v>
+        <v>1.876018067678088e-05</v>
       </c>
       <c r="L26" t="b">
         <v>1</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>5.374307360157132</v>
+        <v>5.650463388468201</v>
       </c>
       <c r="D27" t="n">
-        <v>3.699120814411469</v>
+        <v>3.513842144568969</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>15.32174771287306</v>
+        <v>15.2702683568422</v>
       </c>
       <c r="G27" t="n">
-        <v>2.544745430138366</v>
+        <v>2.614461756474597</v>
       </c>
       <c r="H27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
         <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>1.495590705029455e-07</v>
+        <v>3.512272432473093e-07</v>
       </c>
       <c r="K27" t="n">
-        <v>4.486772115088365e-06</v>
+        <v>1.053681729741928e-05</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,31 +1540,31 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>8.027132295129285</v>
+        <v>7.953848444411787</v>
       </c>
       <c r="D28" t="n">
-        <v>2.654439596667785</v>
+        <v>2.684282381160087</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
-        <v>13.54394667812138</v>
+        <v>13.23202676199851</v>
       </c>
       <c r="G28" t="n">
-        <v>4.022910802501191</v>
+        <v>3.942245673905441</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0001831194665745951</v>
+        <v>0.0003147731734286287</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005493583997237852</v>
+        <v>0.00944319520285886</v>
       </c>
       <c r="L28" t="b">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>7.108069234719775</v>
+        <v>7.266322383270128</v>
       </c>
       <c r="D29" t="n">
-        <v>2.818613854478145</v>
+        <v>2.765774199182629</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
-        <v>18.00231493056317</v>
+        <v>18.05091524027039</v>
       </c>
       <c r="G29" t="n">
-        <v>1.576229772319349</v>
+        <v>1.612336110068456</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K29" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,31 +1620,31 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>9.255704795183071</v>
+        <v>8.925865956119557</v>
       </c>
       <c r="D30" t="n">
-        <v>5.473794696778987</v>
+        <v>5.337698137264181</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>13.97813480146275</v>
+        <v>13.44570428343589</v>
       </c>
       <c r="G30" t="n">
-        <v>4.381578590027509</v>
+        <v>3.947014316344218</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J30" t="n">
-        <v>0.007699105360221116</v>
+        <v>0.007718071325771319</v>
       </c>
       <c r="K30" t="n">
-        <v>0.2309731608066335</v>
+        <v>0.2315421397731396</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1648,31 +1660,31 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.20234606503963</v>
+        <v>10.52202333897254</v>
       </c>
       <c r="D31" t="n">
-        <v>3.363579965256598</v>
+        <v>3.038130036753583</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>14.92124356555809</v>
+        <v>14.98417215915709</v>
       </c>
       <c r="G31" t="n">
-        <v>1.946303785154363</v>
+        <v>1.989355282859982</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J31" t="n">
-        <v>9.288553311355894e-06</v>
+        <v>1.762546939942906e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0002786565993406768</v>
+        <v>0.0005287640819828719</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>68.92259162743773</v>
+        <v>68.26570758135536</v>
       </c>
       <c r="D32" t="n">
-        <v>13.11478568468429</v>
+        <v>12.97600686344074</v>
       </c>
       <c r="E32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F32" t="n">
-        <v>82.87353402422377</v>
+        <v>83.14639124039547</v>
       </c>
       <c r="G32" t="n">
-        <v>4.728265780517907</v>
+        <v>4.742163044943656</v>
       </c>
       <c r="H32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0007183323719422586</v>
+        <v>0.0003499326335598786</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02154997115826776</v>
+        <v>0.01049797900679636</v>
       </c>
       <c r="L32" t="b">
         <v>1</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>68.41535657344849</v>
+        <v>68.47018822049318</v>
       </c>
       <c r="D33" t="n">
-        <v>10.88681341655091</v>
+        <v>11.10792463637869</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>74.74784803171359</v>
+        <v>74.6417264968092</v>
       </c>
       <c r="G33" t="n">
-        <v>5.031942079427445</v>
+        <v>5.168318720433589</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J33" t="n">
-        <v>0.01716686168868725</v>
+        <v>0.02817603999995747</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5150058506606175</v>
+        <v>0.8452811999987241</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>73.6595978935304</v>
+        <v>73.46115714011854</v>
       </c>
       <c r="D34" t="n">
-        <v>8.193457544376379</v>
+        <v>8.303341254475654</v>
       </c>
       <c r="E34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F34" t="n">
-        <v>84.53189614701759</v>
+        <v>83.96765755659584</v>
       </c>
       <c r="G34" t="n">
-        <v>5.608409713982888</v>
+        <v>5.292253070501469</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0001491484485850014</v>
+        <v>0.0003887392872278055</v>
       </c>
       <c r="K34" t="n">
-        <v>0.004474453457550041</v>
+        <v>0.01166217861683417</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,28 +1820,28 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>78.6052760561188</v>
+        <v>78.91119928082816</v>
       </c>
       <c r="D35" t="n">
-        <v>7.435350437118892</v>
+        <v>7.432915229513354</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
-        <v>74.22381848496099</v>
+        <v>74.27647174195131</v>
       </c>
       <c r="G35" t="n">
-        <v>6.050916170409489</v>
+        <v>6.233362290500772</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="J35" t="n">
-        <v>0.04563637859037918</v>
+        <v>0.0453308464290202</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1848,31 +1860,31 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>72.20424549359204</v>
+        <v>72.5813499390875</v>
       </c>
       <c r="D36" t="n">
-        <v>9.425817052928252</v>
+        <v>9.433596919597075</v>
       </c>
       <c r="E36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F36" t="n">
-        <v>82.95756498215576</v>
+        <v>82.89588687712481</v>
       </c>
       <c r="G36" t="n">
-        <v>5.536651821279209</v>
+        <v>5.701381347539431</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J36" t="n">
-        <v>0.000654145800672964</v>
+        <v>0.001429090104558472</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01962437402018892</v>
+        <v>0.04287270313675416</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>78.69177875819462</v>
+        <v>78.69087189870237</v>
       </c>
       <c r="D37" t="n">
-        <v>7.80491152509422</v>
+        <v>7.965853177854501</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>84.76085882644757</v>
+        <v>84.48200363358747</v>
       </c>
       <c r="G37" t="n">
-        <v>3.881415124455318</v>
+        <v>3.832107267930638</v>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01389412783410526</v>
+        <v>0.02817603999995747</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4168238350231577</v>
+        <v>0.8452811999987241</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1928,28 +1940,28 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>72.85592345042124</v>
+        <v>73.33968121618936</v>
       </c>
       <c r="D38" t="n">
-        <v>10.55645762458661</v>
+        <v>10.49912098290403</v>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F38" t="n">
-        <v>78.77024147999894</v>
+        <v>78.43406794411837</v>
       </c>
       <c r="G38" t="n">
-        <v>6.57801010742242</v>
+        <v>6.63727282461226</v>
       </c>
       <c r="H38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09079051029504286</v>
+        <v>0.1632578167047831</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -1968,31 +1980,31 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>62.59491993748634</v>
+        <v>62.42489566331459</v>
       </c>
       <c r="D39" t="n">
-        <v>8.710750977479163</v>
+        <v>8.849634202672767</v>
       </c>
       <c r="E39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>72.71234989656156</v>
+        <v>73.36509439796737</v>
       </c>
       <c r="G39" t="n">
-        <v>7.586195753619495</v>
+        <v>7.341933148567595</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="J39" t="n">
-        <v>0.001136479872569695</v>
+        <v>0.0007196918624463411</v>
       </c>
       <c r="K39" t="n">
-        <v>0.03409439617709084</v>
+        <v>0.02159075587339023</v>
       </c>
       <c r="L39" t="b">
         <v>1</v>
@@ -2008,28 +2020,28 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>71.50725284125522</v>
+        <v>70.82274366539281</v>
       </c>
       <c r="D40" t="n">
-        <v>8.944124437123698</v>
+        <v>8.462668909109295</v>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
-        <v>72.10497916208895</v>
+        <v>72.48130903000953</v>
       </c>
       <c r="G40" t="n">
-        <v>8.05479827903898</v>
+        <v>8.156417742608875</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6083027253155192</v>
+        <v>0.3844926513244845</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -2048,28 +2060,28 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>75.59963296887003</v>
+        <v>75.78849053176079</v>
       </c>
       <c r="D41" t="n">
-        <v>10.57010575001329</v>
+        <v>10.74666243096932</v>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>78.17225957640943</v>
+        <v>78.78164867163416</v>
       </c>
       <c r="G41" t="n">
-        <v>8.243401408209882</v>
+        <v>8.11712601670021</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6083027253155192</v>
+        <v>0.5344829508949708</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>77.07616798768223</v>
+        <v>77.25690682452397</v>
       </c>
       <c r="D42" t="n">
-        <v>9.426819935003095</v>
+        <v>9.578673002841059</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F42" t="n">
-        <v>74.82311529689682</v>
+        <v>74.93390219408137</v>
       </c>
       <c r="G42" t="n">
-        <v>5.533768325678122</v>
+        <v>5.685758555630771</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3836197933949916</v>
+        <v>0.3997653477817533</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>59.47572680955783</v>
+        <v>59.16916813907921</v>
       </c>
       <c r="D43" t="n">
-        <v>7.240594835546708</v>
+        <v>7.229189697118753</v>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
-        <v>81.95097241193763</v>
+        <v>81.97064956979551</v>
       </c>
       <c r="G43" t="n">
-        <v>4.592214397685348</v>
+        <v>4.732850927532971</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K43" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,28 +2180,28 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>77.18943062494094</v>
+        <v>76.91012395742034</v>
       </c>
       <c r="D44" t="n">
-        <v>6.36985349970579</v>
+        <v>6.34943734869467</v>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>79.24282689520301</v>
+        <v>79.42490141036095</v>
       </c>
       <c r="G44" t="n">
-        <v>5.302521241384527</v>
+        <v>5.413913375817218</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="J44" t="n">
-        <v>0.3836197933949916</v>
+        <v>0.2754879695897039</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>66.1394065572559</v>
+        <v>65.70612849262511</v>
       </c>
       <c r="D45" t="n">
-        <v>11.23462059330469</v>
+        <v>11.25977273326289</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>80.5134006384865</v>
+        <v>80.78989265846018</v>
       </c>
       <c r="G45" t="n">
-        <v>6.96494813981945</v>
+        <v>7.088215274060018</v>
       </c>
       <c r="H45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0003338842872497149</v>
+        <v>0.0002829423989985731</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01001652861749145</v>
+        <v>0.008488271969957193</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>66.88819193737943</v>
+        <v>66.93097385952161</v>
       </c>
       <c r="D46" t="n">
-        <v>10.24088160316055</v>
+        <v>10.44986687421483</v>
       </c>
       <c r="E46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
-        <v>81.33828675237987</v>
+        <v>81.53376477204702</v>
       </c>
       <c r="G46" t="n">
-        <v>5.270746399205748</v>
+        <v>5.372845375133715</v>
       </c>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0001091224565023358</v>
+        <v>0.000183385860807171</v>
       </c>
       <c r="K46" t="n">
-        <v>0.003273673695070075</v>
+        <v>0.005501575824215131</v>
       </c>
       <c r="L46" t="b">
         <v>1</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>63.84057037073574</v>
+        <v>63.3685032244561</v>
       </c>
       <c r="D47" t="n">
-        <v>9.357375938296453</v>
+        <v>9.254061443737539</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F47" t="n">
-        <v>81.61710728368219</v>
+        <v>81.19974973906955</v>
       </c>
       <c r="G47" t="n">
-        <v>5.875101365780513</v>
+        <v>5.806283890843315</v>
       </c>
       <c r="H47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>3.105300762762206e-06</v>
+        <v>6.364965065060132e-06</v>
       </c>
       <c r="K47" t="n">
-        <v>9.315902288286618e-05</v>
+        <v>0.000190948951951804</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,28 +2340,28 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>72.0635882858535</v>
+        <v>71.34298829165597</v>
       </c>
       <c r="D48" t="n">
-        <v>12.32519739357394</v>
+        <v>12.05232283763445</v>
       </c>
       <c r="E48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
-        <v>77.30116052623849</v>
+        <v>77.02832963721391</v>
       </c>
       <c r="G48" t="n">
-        <v>5.833161038908295</v>
+        <v>5.906517958099478</v>
       </c>
       <c r="H48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2934330149772345</v>
+        <v>0.2519080940857671</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>75.56841504822337</v>
+        <v>75.24845626176331</v>
       </c>
       <c r="D49" t="n">
-        <v>7.968901923906376</v>
+        <v>7.974335844343535</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
-        <v>85.23918815693995</v>
+        <v>86.06646536060747</v>
       </c>
       <c r="G49" t="n">
-        <v>7.387997152951846</v>
+        <v>6.808767846221572</v>
       </c>
       <c r="H49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0003025476445782702</v>
+        <v>0.0001314683458180165</v>
       </c>
       <c r="K49" t="n">
-        <v>0.009076429337348106</v>
+        <v>0.003944050374540494</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.92277427941994</v>
+        <v>75.7544899169019</v>
       </c>
       <c r="D50" t="n">
-        <v>8.026778020346585</v>
+        <v>8.148970688316806</v>
       </c>
       <c r="E50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F50" t="n">
-        <v>87.05667145265431</v>
+        <v>87.06286769345317</v>
       </c>
       <c r="G50" t="n">
-        <v>4.419163387813026</v>
+        <v>4.555097713101023</v>
       </c>
       <c r="H50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J50" t="n">
-        <v>1.486998015493185e-05</v>
+        <v>2.882017313833171e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0004460994046479555</v>
+        <v>0.0008646051941499513</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>65.9959206828558</v>
+        <v>65.63523844880041</v>
       </c>
       <c r="D51" t="n">
-        <v>7.851460696356444</v>
+        <v>7.807797577536516</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
-        <v>77.77990049976358</v>
+        <v>77.83404773244115</v>
       </c>
       <c r="G51" t="n">
-        <v>5.009772127030915</v>
+        <v>5.159126633923759</v>
       </c>
       <c r="H51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J51" t="n">
-        <v>9.288553311355894e-06</v>
+        <v>1.2096061063117e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0002786565993406768</v>
+        <v>0.00036288183189351</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,28 +2500,28 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>76.26842158023931</v>
+        <v>76.24170354151505</v>
       </c>
       <c r="D52" t="n">
-        <v>7.091211105206835</v>
+        <v>7.236204004026258</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
-        <v>77.8940147292775</v>
+        <v>77.60698058154216</v>
       </c>
       <c r="G52" t="n">
-        <v>9.351041150156346</v>
+        <v>9.565902336972066</v>
       </c>
       <c r="H52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0.8793104914768145</v>
       </c>
       <c r="K52" t="n">
         <v>1</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>73.33237134863874</v>
+        <v>73.64384121221529</v>
       </c>
       <c r="D53" t="n">
-        <v>9.342640603705968</v>
+        <v>9.407256176972624</v>
       </c>
       <c r="E53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>84.05018168018449</v>
+        <v>84.11067689310001</v>
       </c>
       <c r="G53" t="n">
-        <v>3.879212693718593</v>
+        <v>3.99081381612133</v>
       </c>
       <c r="H53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J53" t="n">
-        <v>0.000654145800672964</v>
+        <v>0.00117894338145478</v>
       </c>
       <c r="K53" t="n">
-        <v>0.01962437402018892</v>
+        <v>0.03536830144364341</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,34 +2580,34 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>65.3406333405613</v>
+        <v>65.41779226045117</v>
       </c>
       <c r="D54" t="n">
-        <v>7.191663947650017</v>
+        <v>7.329815422434716</v>
       </c>
       <c r="E54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>73.63729697458865</v>
+        <v>73.22544599438365</v>
       </c>
       <c r="G54" t="n">
-        <v>6.367898364092721</v>
+        <v>6.340422049489229</v>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0007183323719422586</v>
+        <v>0.001727381249630609</v>
       </c>
       <c r="K54" t="n">
-        <v>0.02154997115826776</v>
+        <v>0.05182143748891828</v>
       </c>
       <c r="L54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>63.73609724236248</v>
+        <v>63.39213215607163</v>
       </c>
       <c r="D55" t="n">
-        <v>14.23463422329101</v>
+        <v>14.42600819472124</v>
       </c>
       <c r="E55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
-        <v>76.70596622500724</v>
+        <v>76.73369221877371</v>
       </c>
       <c r="G55" t="n">
-        <v>7.477474555700343</v>
+        <v>7.706756543250013</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="J55" t="n">
-        <v>0.009650320070671655</v>
+        <v>0.01153296995901035</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2895096021201496</v>
+        <v>0.3459890987703106</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>55.39152724490607</v>
+        <v>55.66131058107803</v>
       </c>
       <c r="D56" t="n">
-        <v>9.618739823967115</v>
+        <v>9.723969666807088</v>
       </c>
       <c r="E56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>74.47069826046769</v>
+        <v>74.45058814066124</v>
       </c>
       <c r="G56" t="n">
-        <v>3.376009780886836</v>
+        <v>3.478923264541357</v>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>1.278267744062503e-06</v>
+        <v>2.875249886287048e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>3.83480323218751e-05</v>
+        <v>8.625749658861143e-05</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,34 +2700,34 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>68.64018164236893</v>
+        <v>68.23620656487172</v>
       </c>
       <c r="D57" t="n">
-        <v>10.64602819113225</v>
+        <v>10.6761618965967</v>
       </c>
       <c r="E57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
-        <v>79.43845952105464</v>
+        <v>79.80934663831974</v>
       </c>
       <c r="G57" t="n">
-        <v>5.573850147386499</v>
+        <v>5.538146801350705</v>
       </c>
       <c r="H57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="J57" t="n">
-        <v>0.001770593944294099</v>
+        <v>0.00117894338145478</v>
       </c>
       <c r="K57" t="n">
-        <v>0.05311781832882298</v>
+        <v>0.03536830144364341</v>
       </c>
       <c r="L57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>70.46922200420943</v>
+        <v>70.28852553876784</v>
       </c>
       <c r="D58" t="n">
-        <v>9.041996140149807</v>
+        <v>9.184115878761034</v>
       </c>
       <c r="E58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>82.21849925908498</v>
+        <v>82.93340114365108</v>
       </c>
       <c r="G58" t="n">
-        <v>5.29527573099731</v>
+        <v>4.593909191150786</v>
       </c>
       <c r="H58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0001091224565023358</v>
+        <v>6.625770668464903e-05</v>
       </c>
       <c r="K58" t="n">
-        <v>0.003273673695070075</v>
+        <v>0.001987731200539471</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>77.46126242880725</v>
+        <v>78.23047793848546</v>
       </c>
       <c r="D59" t="n">
-        <v>9.068815517930757</v>
+        <v>8.418902027231219</v>
       </c>
       <c r="E59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F59" t="n">
-        <v>74.94437366438781</v>
+        <v>75.36377079409291</v>
       </c>
       <c r="G59" t="n">
-        <v>4.54691221018588</v>
+        <v>4.356186878647478</v>
       </c>
       <c r="H59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I59" t="n">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1241725989660121</v>
+        <v>0.09486460481682263</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>71.44407813272188</v>
+        <v>72.08391922351615</v>
       </c>
       <c r="D60" t="n">
-        <v>10.62005112393661</v>
+        <v>10.35615592694026</v>
       </c>
       <c r="E60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
-        <v>79.00272506483084</v>
+        <v>80.00773520723611</v>
       </c>
       <c r="G60" t="n">
-        <v>7.873755518578752</v>
+        <v>6.978538960377734</v>
       </c>
       <c r="H60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I60" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02939745744471163</v>
+        <v>0.02115212229111062</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8819237233413491</v>
+        <v>0.6345636687333186</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>67.10033224772313</v>
+        <v>67.8499284778368</v>
       </c>
       <c r="D61" t="n">
-        <v>9.451987564906915</v>
+        <v>8.889049954528591</v>
       </c>
       <c r="E61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
-        <v>79.44306276200112</v>
+        <v>78.88291414772547</v>
       </c>
       <c r="G61" t="n">
-        <v>6.886680089954631</v>
+        <v>6.71241240810186</v>
       </c>
       <c r="H61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0001831194665745951</v>
+        <v>0.0004787061564288396</v>
       </c>
       <c r="K61" t="n">
-        <v>0.005493583997237852</v>
+        <v>0.01436118469286519</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>92.13431615709804</v>
+        <v>90.96568097338792</v>
       </c>
       <c r="D62" t="n">
-        <v>21.24808953059546</v>
+        <v>20.8842123404478</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
-        <v>94.6736550168133</v>
+        <v>95.44877851004827</v>
       </c>
       <c r="G62" t="n">
-        <v>13.30736764295058</v>
+        <v>13.33941645566578</v>
       </c>
       <c r="H62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I62" t="n">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="J62" t="n">
-        <v>0.6446207339155774</v>
+        <v>0.4477229127520573</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>105.9457982354019</v>
+        <v>105.0897740385594</v>
       </c>
       <c r="D63" t="n">
-        <v>13.44599062661587</v>
+        <v>13.03872460360568</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
-        <v>48.58251657013515</v>
+        <v>49.16560604435998</v>
       </c>
       <c r="G63" t="n">
-        <v>8.819781592757383</v>
+        <v>8.767579190332862</v>
       </c>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I63" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J63" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K63" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>110.253411310581</v>
+        <v>110.240778878949</v>
       </c>
       <c r="D64" t="n">
-        <v>8.230141007380807</v>
+        <v>8.399615016070966</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
-        <v>127.118268866887</v>
+        <v>126.6535888387656</v>
       </c>
       <c r="G64" t="n">
-        <v>10.82393657825161</v>
+        <v>10.99132318037934</v>
       </c>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J64" t="n">
-        <v>3.306911779113734e-05</v>
+        <v>8.350097704504365e-05</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0009920735337341201</v>
+        <v>0.00250502931135131</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>122.7036835365475</v>
+        <v>122.795968320466</v>
       </c>
       <c r="D65" t="n">
-        <v>9.427166257825132</v>
+        <v>9.6104905843198</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
-        <v>35.08880925692985</v>
+        <v>34.98901338766002</v>
       </c>
       <c r="G65" t="n">
-        <v>7.722869962350998</v>
+        <v>7.949910931573276</v>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J65" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K65" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>107.1897333496718</v>
+        <v>106.6616231899594</v>
       </c>
       <c r="D66" t="n">
-        <v>13.80638299231615</v>
+        <v>13.84146108434731</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>101.3039953938806</v>
+        <v>102.4294065161446</v>
       </c>
       <c r="G66" t="n">
-        <v>15.43196531634667</v>
+        <v>15.21506810107243</v>
       </c>
       <c r="H66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66" t="n">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1441201767292509</v>
+        <v>0.2635160866220128</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,28 +3100,28 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>125.7840325960414</v>
+        <v>126.1072584145166</v>
       </c>
       <c r="D67" t="n">
-        <v>7.689294913321273</v>
+        <v>7.679644221260455</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" t="n">
-        <v>118.0371461163346</v>
+        <v>119.3759541005447</v>
       </c>
       <c r="G67" t="n">
-        <v>12.54074938751271</v>
+        <v>11.6888356556367</v>
       </c>
       <c r="H67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" t="n">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="J67" t="n">
-        <v>0.08600341800722716</v>
+        <v>0.1187964420955191</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>93.00058427792393</v>
+        <v>93.7326850759755</v>
       </c>
       <c r="D68" t="n">
-        <v>20.5126902173637</v>
+        <v>20.61318201998173</v>
       </c>
       <c r="E68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
-        <v>91.81306085267251</v>
+        <v>92.1150096118496</v>
       </c>
       <c r="G68" t="n">
-        <v>12.85034425886945</v>
+        <v>13.18719511081903</v>
       </c>
       <c r="H68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9795565369815412</v>
+        <v>0.9889863985623705</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>75.5220296550456</v>
+        <v>74.55519333476293</v>
       </c>
       <c r="D69" t="n">
-        <v>15.45849551570614</v>
+        <v>15.01841037984302</v>
       </c>
       <c r="E69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
-        <v>55.19231529570344</v>
+        <v>56.58700696188956</v>
       </c>
       <c r="G69" t="n">
-        <v>21.63622855733265</v>
+        <v>21.54800415301415</v>
       </c>
       <c r="H69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I69" t="n">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="J69" t="n">
-        <v>0.002953980125120048</v>
+        <v>0.008375319316666029</v>
       </c>
       <c r="K69" t="n">
-        <v>0.08861940375360144</v>
+        <v>0.2512595794999809</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3208,31 +3220,31 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>105.4708180871267</v>
+        <v>104.346868043216</v>
       </c>
       <c r="D70" t="n">
-        <v>16.27760600203077</v>
+        <v>15.63390174190046</v>
       </c>
       <c r="E70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>45.54940585388002</v>
+        <v>45.36832273221611</v>
       </c>
       <c r="G70" t="n">
-        <v>11.38058815624803</v>
+        <v>11.70705769217184</v>
       </c>
       <c r="H70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I70" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J70" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K70" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L70" t="b">
         <v>1</v>
@@ -3248,31 +3260,31 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>115.5352085656512</v>
+        <v>116.5756277061246</v>
       </c>
       <c r="D71" t="n">
-        <v>15.88215729411955</v>
+        <v>15.3522389995195</v>
       </c>
       <c r="E71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
-        <v>83.45790987432271</v>
+        <v>85.45634353363748</v>
       </c>
       <c r="G71" t="n">
-        <v>26.45749884395204</v>
+        <v>25.9972242240106</v>
       </c>
       <c r="H71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I71" t="n">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0002242686119078368</v>
+        <v>0.0002281177205721503</v>
       </c>
       <c r="K71" t="n">
-        <v>0.006728058357235105</v>
+        <v>0.006843531617164509</v>
       </c>
       <c r="L71" t="b">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>121.136531094908</v>
+        <v>121.0263198103666</v>
       </c>
       <c r="D72" t="n">
-        <v>12.06795480085127</v>
+        <v>12.304471427325</v>
       </c>
       <c r="E72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
-        <v>63.44349520826648</v>
+        <v>62.47483246277798</v>
       </c>
       <c r="G72" t="n">
-        <v>12.23363193154437</v>
+        <v>11.96095238180594</v>
       </c>
       <c r="H72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I72" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J72" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K72" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>54.66332081367562</v>
+        <v>53.05808748442698</v>
       </c>
       <c r="D73" t="n">
-        <v>22.42557011295096</v>
+        <v>21.43458113994147</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
-        <v>108.2623753410435</v>
+        <v>108.1855253584336</v>
       </c>
       <c r="G73" t="n">
-        <v>9.687119964913778</v>
+        <v>9.980225994609748</v>
       </c>
       <c r="H73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>9.822566872680135e-08</v>
+        <v>1.949540650556156e-07</v>
       </c>
       <c r="K73" t="n">
-        <v>2.946770061804041e-06</v>
+        <v>5.848621951668467e-06</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>125.4448970038595</v>
+        <v>125.2088411147188</v>
       </c>
       <c r="D74" t="n">
-        <v>5.640904025103989</v>
+        <v>5.634941310815476</v>
       </c>
       <c r="E74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>93.32305807746764</v>
+        <v>94.18942983732592</v>
       </c>
       <c r="G74" t="n">
-        <v>11.74416160264419</v>
+        <v>11.56656667021712</v>
       </c>
       <c r="H74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I74" t="n">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="J74" t="n">
-        <v>6.41425315746474e-08</v>
+        <v>1.446036855623673e-07</v>
       </c>
       <c r="K74" t="n">
-        <v>1.924275947239422e-06</v>
+        <v>4.338110566871019e-06</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>85.00259463268172</v>
+        <v>84.4615159661376</v>
       </c>
       <c r="D75" t="n">
-        <v>17.58801046550078</v>
+        <v>17.74564867947753</v>
       </c>
       <c r="E75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
-        <v>65.13361881300523</v>
+        <v>64.27988088582188</v>
       </c>
       <c r="G75" t="n">
-        <v>13.06482370385334</v>
+        <v>12.99872901257176</v>
       </c>
       <c r="H75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I75" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0009476982734722665</v>
+        <v>0.00117894338145478</v>
       </c>
       <c r="K75" t="n">
-        <v>0.028430948204168</v>
+        <v>0.03536830144364341</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,31 +3460,31 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>86.86245107530159</v>
+        <v>86.35376342850707</v>
       </c>
       <c r="D76" t="n">
-        <v>17.65276100741631</v>
+        <v>17.83634095326067</v>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
-        <v>100.8665089545404</v>
+        <v>100.7132336215609</v>
       </c>
       <c r="G76" t="n">
-        <v>6.918820897874459</v>
+        <v>7.103701585055397</v>
       </c>
       <c r="H76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I76" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0034864458212706</v>
+        <v>0.003913842977766814</v>
       </c>
       <c r="K76" t="n">
-        <v>0.104593374638118</v>
+        <v>0.1174152893330044</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>70.54544121071007</v>
+        <v>69.24911093580862</v>
       </c>
       <c r="D77" t="n">
-        <v>17.49392032698178</v>
+        <v>16.63661611876296</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>100.0187042496673</v>
+        <v>99.47968156439536</v>
       </c>
       <c r="G77" t="n">
-        <v>12.16090387716031</v>
+        <v>12.33658317018276</v>
       </c>
       <c r="H77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I77" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>3.516194464852719e-06</v>
+        <v>1.913423550711778e-06</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0001054858339455816</v>
+        <v>5.740270652135333e-05</v>
       </c>
       <c r="L77" t="b">
         <v>1</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>102.0012847252003</v>
+        <v>102.2822935813775</v>
       </c>
       <c r="D78" t="n">
-        <v>12.03045799204945</v>
+        <v>12.19787959905273</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
-        <v>72.9327901260375</v>
+        <v>73.33659711797679</v>
       </c>
       <c r="G78" t="n">
-        <v>14.61379026518651</v>
+        <v>14.97125657919117</v>
       </c>
       <c r="H78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I78" t="n">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="J78" t="n">
-        <v>3.516194464852719e-06</v>
+        <v>8.246867290450602e-06</v>
       </c>
       <c r="K78" t="n">
-        <v>0.0001054858339455816</v>
+        <v>0.000247406018713518</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,28 +3580,28 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>107.9725444519327</v>
+        <v>108.1585993505296</v>
       </c>
       <c r="D79" t="n">
-        <v>11.92547607995181</v>
+        <v>12.13578495978325</v>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
-        <v>101.8693299322053</v>
+        <v>106.1340212571224</v>
       </c>
       <c r="G79" t="n">
-        <v>39.13227360848551</v>
+        <v>36.30226163042708</v>
       </c>
       <c r="H79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I79" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="J79" t="n">
-        <v>0.2595332729961103</v>
+        <v>0.1472220627556302</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>82.86762502297641</v>
+        <v>83.47998226977501</v>
       </c>
       <c r="D80" t="n">
-        <v>13.64946396855218</v>
+        <v>13.59029651855821</v>
       </c>
       <c r="E80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
-        <v>111.435712650969</v>
+        <v>111.9184723668889</v>
       </c>
       <c r="G80" t="n">
-        <v>14.37795213155412</v>
+        <v>14.68618002339219</v>
       </c>
       <c r="H80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I80" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J80" t="n">
-        <v>8.244668028301287e-06</v>
+        <v>1.555819255073262e-05</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0002473400408490386</v>
+        <v>0.0004667457765219786</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>88.31552349733458</v>
+        <v>87.04304921573419</v>
       </c>
       <c r="D81" t="n">
-        <v>16.77075257370988</v>
+        <v>15.8901686964171</v>
       </c>
       <c r="E81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F81" t="n">
-        <v>51.09755133227846</v>
+        <v>51.06033618497636</v>
       </c>
       <c r="G81" t="n">
-        <v>7.169481797374423</v>
+        <v>7.388539546375536</v>
       </c>
       <c r="H81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I81" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J81" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K81" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,34 +3700,34 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>113.8888647141714</v>
+        <v>114.3516404606535</v>
       </c>
       <c r="D82" t="n">
-        <v>11.76050244046544</v>
+        <v>11.77787227244669</v>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
-        <v>57.81772995455132</v>
+        <v>58.29890641275024</v>
       </c>
       <c r="G82" t="n">
-        <v>41.55426719443279</v>
+        <v>42.78718755502323</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I82" t="n">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="J82" t="n">
-        <v>0.001038124885353655</v>
+        <v>0.001897094078176322</v>
       </c>
       <c r="K82" t="n">
-        <v>0.03114374656060966</v>
+        <v>0.05691282234528967</v>
       </c>
       <c r="L82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -3728,28 +3740,28 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>98.4586018013599</v>
+        <v>98.89683198282346</v>
       </c>
       <c r="D83" t="n">
-        <v>21.94067361438379</v>
+        <v>22.28564705435951</v>
       </c>
       <c r="E83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
-        <v>104.9901885697601</v>
+        <v>105.643605439311</v>
       </c>
       <c r="G83" t="n">
-        <v>13.44564523621158</v>
+        <v>13.59508185023738</v>
       </c>
       <c r="H83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I83" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="J83" t="n">
-        <v>0.3301828491688743</v>
+        <v>0.3844926513244845</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -3768,31 +3780,31 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>79.16314735616686</v>
+        <v>78.12267592365659</v>
       </c>
       <c r="D84" t="n">
-        <v>17.06213798134827</v>
+        <v>16.61872103387499</v>
       </c>
       <c r="E84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
-        <v>61.8740333637284</v>
+        <v>60.80813177807728</v>
       </c>
       <c r="G84" t="n">
-        <v>11.29748035836955</v>
+        <v>10.78404579069189</v>
       </c>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I84" t="n">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="J84" t="n">
-        <v>0.001485579758789372</v>
+        <v>0.001571732149984825</v>
       </c>
       <c r="K84" t="n">
-        <v>0.04456739276368115</v>
+        <v>0.04715196449954475</v>
       </c>
       <c r="L84" t="b">
         <v>1</v>
@@ -3808,28 +3820,28 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>65.15921224189688</v>
+        <v>64.83852437044293</v>
       </c>
       <c r="D85" t="n">
-        <v>18.3665019039316</v>
+        <v>18.676528694839</v>
       </c>
       <c r="E85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>54.29850571439895</v>
+        <v>55.35076396973221</v>
       </c>
       <c r="G85" t="n">
-        <v>15.92626390745491</v>
+        <v>15.83273644280833</v>
       </c>
       <c r="H85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I85" t="n">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="J85" t="n">
-        <v>0.06139823826300086</v>
+        <v>0.1124100413252736</v>
       </c>
       <c r="K85" t="n">
         <v>1</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>46.52119992647505</v>
+        <v>45.78211698118983</v>
       </c>
       <c r="D86" t="n">
-        <v>12.12342202053777</v>
+        <v>11.808697143057</v>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F86" t="n">
-        <v>53.88172852009497</v>
+        <v>52.09274018136141</v>
       </c>
       <c r="G86" t="n">
-        <v>17.56930277726237</v>
+        <v>16.53979375294457</v>
       </c>
       <c r="H86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J86" t="n">
-        <v>0.2818176174262974</v>
+        <v>0.3550366386519953</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>87.88211525029095</v>
+        <v>87.73426956324154</v>
       </c>
       <c r="D87" t="n">
-        <v>11.85767204259461</v>
+        <v>12.07958789383247</v>
       </c>
       <c r="E87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
-        <v>63.8167674630663</v>
+        <v>62.94400963482624</v>
       </c>
       <c r="G87" t="n">
-        <v>9.984542071565865</v>
+        <v>9.642238694811759</v>
       </c>
       <c r="H87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I87" t="n">
-        <v>390</v>
+        <v>354</v>
       </c>
       <c r="J87" t="n">
-        <v>5.74386748864156e-06</v>
+        <v>8.246867290450602e-06</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0001723160246592468</v>
+        <v>0.000247406018713518</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,28 +3940,28 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>103.533644629618</v>
+        <v>103.0334735540099</v>
       </c>
       <c r="D88" t="n">
-        <v>20.68997623787331</v>
+        <v>20.96800663627118</v>
       </c>
       <c r="E88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
-        <v>103.9406350353384</v>
+        <v>107.2774266091228</v>
       </c>
       <c r="G88" t="n">
-        <v>32.64158018857177</v>
+        <v>30.70478429195461</v>
       </c>
       <c r="H88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I88" t="n">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5729260016107649</v>
+        <v>0.3408577040488102</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>121.4833861895713</v>
+        <v>121.9548486229393</v>
       </c>
       <c r="D89" t="n">
-        <v>9.730142088235228</v>
+        <v>9.646945826669636</v>
       </c>
       <c r="E89" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>61.13482449532718</v>
+        <v>59.6227296313032</v>
       </c>
       <c r="G89" t="n">
-        <v>9.637935427553293</v>
+        <v>7.734732499547842</v>
       </c>
       <c r="H89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I89" t="n">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J89" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K89" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,28 +4020,28 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>108.857073096011</v>
+        <v>108.9306577160302</v>
       </c>
       <c r="D90" t="n">
-        <v>19.14916092623896</v>
+        <v>19.54056708351981</v>
       </c>
       <c r="E90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F90" t="n">
-        <v>93.52656357561679</v>
+        <v>96.8002511143615</v>
       </c>
       <c r="G90" t="n">
-        <v>29.59355981827722</v>
+        <v>27.35553773763498</v>
       </c>
       <c r="H90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I90" t="n">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="J90" t="n">
-        <v>0.1826978999929049</v>
+        <v>0.2754879695897039</v>
       </c>
       <c r="K90" t="n">
         <v>1</v>
@@ -4048,31 +4060,31 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>72.53933472213703</v>
+        <v>72.33238204103087</v>
       </c>
       <c r="D91" t="n">
-        <v>15.23635681124465</v>
+        <v>15.51607576926108</v>
       </c>
       <c r="E91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
-        <v>91.29000872207207</v>
+        <v>90.21401779149545</v>
       </c>
       <c r="G91" t="n">
-        <v>11.00676852733554</v>
+        <v>10.44216944878444</v>
       </c>
       <c r="H91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I91" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0002242686119078368</v>
+        <v>0.000530647383889581</v>
       </c>
       <c r="K91" t="n">
-        <v>0.006728058357235105</v>
+        <v>0.01591942151668743</v>
       </c>
       <c r="L91" t="b">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>10.6304884512797</v>
+        <v>10.84948942313146</v>
       </c>
       <c r="D92" t="n">
-        <v>4.250897736371052</v>
+        <v>4.1980969583645</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
-        <v>11.5791901040536</v>
+        <v>11.30288230307583</v>
       </c>
       <c r="G92" t="n">
-        <v>1.589807628491486</v>
+        <v>1.177953436730577</v>
       </c>
       <c r="H92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I92" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J92" t="n">
-        <v>0.6263484608675448</v>
+        <v>0.9889863985623705</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>7.807742409624862</v>
+        <v>7.885661875981292</v>
       </c>
       <c r="D93" t="n">
-        <v>2.251097684799823</v>
+        <v>2.264243377308186</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
-        <v>16.87330165878276</v>
+        <v>16.54097188723678</v>
       </c>
       <c r="G93" t="n">
-        <v>2.174781115927239</v>
+        <v>1.774188588801128</v>
       </c>
       <c r="H93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K93" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L93" t="b">
         <v>1</v>
@@ -4168,31 +4180,31 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>9.965008228817865</v>
+        <v>10.00544166051868</v>
       </c>
       <c r="D94" t="n">
-        <v>3.014493044084149</v>
+        <v>3.070004684994597</v>
       </c>
       <c r="E94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
-        <v>13.84632265311772</v>
+        <v>13.69110711296176</v>
       </c>
       <c r="G94" t="n">
-        <v>2.990828999899988</v>
+        <v>3.015719242885107</v>
       </c>
       <c r="H94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I94" t="n">
         <v>77</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0005414616502312927</v>
+        <v>0.001571732149984825</v>
       </c>
       <c r="K94" t="n">
-        <v>0.01624384950693878</v>
+        <v>0.04715196449954475</v>
       </c>
       <c r="L94" t="b">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>9.842500822881762</v>
+        <v>9.771026757845727</v>
       </c>
       <c r="D95" t="n">
-        <v>3.000729822424213</v>
+        <v>3.041685124345728</v>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
-        <v>19.33868929786312</v>
+        <v>19.38184987018325</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9976762445780778</v>
+        <v>1.012867001144087</v>
       </c>
       <c r="H95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K95" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,31 +4260,31 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>11.92818188525052</v>
+        <v>12.17440559796073</v>
       </c>
       <c r="D96" t="n">
-        <v>3.756365524406491</v>
+        <v>3.630779179478678</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F96" t="n">
-        <v>16.04634159775932</v>
+        <v>16.22196651012992</v>
       </c>
       <c r="G96" t="n">
-        <v>2.308199994040491</v>
+        <v>2.266368029667947</v>
       </c>
       <c r="H96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I96" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0008646155021806337</v>
+        <v>0.0009698089490143557</v>
       </c>
       <c r="K96" t="n">
-        <v>0.02593846506541901</v>
+        <v>0.02909426847043067</v>
       </c>
       <c r="L96" t="b">
         <v>1</v>
@@ -4288,31 +4300,31 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>7.587508143692173</v>
+        <v>7.555814203696333</v>
       </c>
       <c r="D97" t="n">
-        <v>2.85555778301174</v>
+        <v>2.910129957031538</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F97" t="n">
-        <v>11.6356955437529</v>
+        <v>11.50476562056633</v>
       </c>
       <c r="G97" t="n">
-        <v>1.242348175595038</v>
+        <v>1.16123569523426</v>
       </c>
       <c r="H97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I97" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J97" t="n">
-        <v>2.102378783512399e-05</v>
+        <v>5.242268104861639e-05</v>
       </c>
       <c r="K97" t="n">
-        <v>0.0006307136350537198</v>
+        <v>0.001572680431458492</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
@@ -4328,31 +4340,31 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>9.618191022075907</v>
+        <v>9.711346310273699</v>
       </c>
       <c r="D98" t="n">
-        <v>1.959071197374247</v>
+        <v>1.94446066084752</v>
       </c>
       <c r="E98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F98" t="n">
-        <v>16.42838132642531</v>
+        <v>16.27894522161053</v>
       </c>
       <c r="G98" t="n">
-        <v>2.025309351716328</v>
+        <v>1.994646786553036</v>
       </c>
       <c r="H98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K98" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L98" t="b">
         <v>1</v>
@@ -4368,31 +4380,31 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>10.39383758016</v>
+        <v>10.65529269053966</v>
       </c>
       <c r="D99" t="n">
-        <v>4.321292456447123</v>
+        <v>4.212204230504334</v>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F99" t="n">
-        <v>16.34071629105642</v>
+        <v>16.31348595071217</v>
       </c>
       <c r="G99" t="n">
-        <v>1.906251920116522</v>
+        <v>1.961709280826978</v>
       </c>
       <c r="H99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I99" t="n">
         <v>36</v>
       </c>
       <c r="J99" t="n">
-        <v>6.483379479788684e-06</v>
+        <v>1.762546939942906e-05</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0001945013843936605</v>
+        <v>0.0005287640819828719</v>
       </c>
       <c r="L99" t="b">
         <v>1</v>
@@ -4408,31 +4420,31 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>10.91726354917426</v>
+        <v>11.11470268666172</v>
       </c>
       <c r="D100" t="n">
-        <v>3.625567333391776</v>
+        <v>3.56621376262032</v>
       </c>
       <c r="E100" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F100" t="n">
-        <v>17.17483700931704</v>
+        <v>16.98504962119058</v>
       </c>
       <c r="G100" t="n">
-        <v>2.025604420191244</v>
+        <v>1.935765494715264</v>
       </c>
       <c r="H100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I100" t="n">
         <v>32</v>
       </c>
       <c r="J100" t="n">
-        <v>3.978940755743726e-06</v>
+        <v>1.065393582908646e-05</v>
       </c>
       <c r="K100" t="n">
-        <v>0.0001193682226723118</v>
+        <v>0.0003196180748725937</v>
       </c>
       <c r="L100" t="b">
         <v>1</v>
@@ -4448,31 +4460,31 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>10.8681069746325</v>
+        <v>10.79676120348822</v>
       </c>
       <c r="D101" t="n">
-        <v>2.264158934085291</v>
+        <v>2.283147138398487</v>
       </c>
       <c r="E101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F101" t="n">
-        <v>17.09924530222959</v>
+        <v>16.91838528956922</v>
       </c>
       <c r="G101" t="n">
-        <v>3.510772663280882</v>
+        <v>3.54115717464168</v>
       </c>
       <c r="H101" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I101" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J101" t="n">
-        <v>7.313484223787676e-06</v>
+        <v>1.372335445382672e-05</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0002194045267136303</v>
+        <v>0.0004117006336148015</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>9.833966971227486</v>
+        <v>10.04713197321375</v>
       </c>
       <c r="D102" t="n">
-        <v>3.944572841726642</v>
+        <v>3.882266207540719</v>
       </c>
       <c r="E102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F102" t="n">
-        <v>19.02182005428011</v>
+        <v>18.93373974944664</v>
       </c>
       <c r="G102" t="n">
-        <v>1.382810836836604</v>
+        <v>1.37832789710389</v>
       </c>
       <c r="H102" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K102" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>14.70474235287437</v>
+        <v>14.85883539763157</v>
       </c>
       <c r="D103" t="n">
-        <v>2.637105918289557</v>
+        <v>2.578851413754921</v>
       </c>
       <c r="E103" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F103" t="n">
-        <v>13.44413400454666</v>
+        <v>13.59502254057653</v>
       </c>
       <c r="G103" t="n">
-        <v>1.814167169383861</v>
+        <v>1.763478868794746</v>
       </c>
       <c r="H103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I103" t="n">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="J103" t="n">
-        <v>0.09079051029504286</v>
+        <v>0.07958476178631996</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,34 +4580,34 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>9.45294733556549</v>
+        <v>9.610764026824027</v>
       </c>
       <c r="D104" t="n">
-        <v>2.791392871212851</v>
+        <v>2.737495732208036</v>
       </c>
       <c r="E104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F104" t="n">
-        <v>14.48170623620877</v>
+        <v>14.1390643621247</v>
       </c>
       <c r="G104" t="n">
-        <v>4.337791627138424</v>
+        <v>4.242240533858547</v>
       </c>
       <c r="H104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I104" t="n">
         <v>81</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0007883302594397486</v>
+        <v>0.002283306890774047</v>
       </c>
       <c r="K104" t="n">
-        <v>0.02364990778319246</v>
+        <v>0.06849920672322141</v>
       </c>
       <c r="L104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4608,31 +4620,31 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>13.88858282730828</v>
+        <v>13.93098794289006</v>
       </c>
       <c r="D105" t="n">
-        <v>1.708942675662555</v>
+        <v>1.73124726739874</v>
       </c>
       <c r="E105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F105" t="n">
-        <v>16.60777381266332</v>
+        <v>16.78112967127286</v>
       </c>
       <c r="G105" t="n">
-        <v>1.497284473731844</v>
+        <v>1.367877473255941</v>
       </c>
       <c r="H105" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I105" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J105" t="n">
-        <v>2.356666862382452e-05</v>
+        <v>1.065393582908646e-05</v>
       </c>
       <c r="K105" t="n">
-        <v>0.0007070000587147356</v>
+        <v>0.0003196180748725937</v>
       </c>
       <c r="L105" t="b">
         <v>1</v>
@@ -4648,31 +4660,31 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>11.15224731854035</v>
+        <v>11.24995111183622</v>
       </c>
       <c r="D106" t="n">
-        <v>2.997443350746936</v>
+        <v>3.019996187144279</v>
       </c>
       <c r="E106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F106" t="n">
-        <v>14.47192988312737</v>
+        <v>14.45234148884848</v>
       </c>
       <c r="G106" t="n">
-        <v>1.182847788998398</v>
+        <v>1.216573655578373</v>
       </c>
       <c r="H106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I106" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0003338842872497149</v>
+        <v>0.0007196918624463411</v>
       </c>
       <c r="K106" t="n">
-        <v>0.01001652861749145</v>
+        <v>0.02159075587339023</v>
       </c>
       <c r="L106" t="b">
         <v>1</v>
@@ -4688,31 +4700,31 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.34535616593832</v>
+        <v>13.34340411771934</v>
       </c>
       <c r="D107" t="n">
-        <v>2.861160661166492</v>
+        <v>2.920143560467942</v>
       </c>
       <c r="E107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F107" t="n">
-        <v>17.04705882352938</v>
+        <v>16.97347642727424</v>
       </c>
       <c r="G107" t="n">
-        <v>2.645875367070657</v>
+        <v>2.710378795121398</v>
       </c>
       <c r="H107" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I107" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J107" t="n">
-        <v>0.0004058747458892882</v>
+        <v>0.0009698089490143557</v>
       </c>
       <c r="K107" t="n">
-        <v>0.01217624237667865</v>
+        <v>0.02909426847043067</v>
       </c>
       <c r="L107" t="b">
         <v>1</v>
@@ -4728,31 +4740,31 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>9.59567652233129</v>
+        <v>9.689453930442824</v>
       </c>
       <c r="D108" t="n">
-        <v>3.707761869344382</v>
+        <v>3.755057315534797</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F108" t="n">
-        <v>16.47974183544363</v>
+        <v>16.33482527949601</v>
       </c>
       <c r="G108" t="n">
-        <v>2.714858404476399</v>
+        <v>2.733879281705243</v>
       </c>
       <c r="H108" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I108" t="n">
         <v>39</v>
       </c>
       <c r="J108" t="n">
-        <v>9.288553311355894e-06</v>
+        <v>2.551425383401997e-05</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0002786565993406768</v>
+        <v>0.000765427615020599</v>
       </c>
       <c r="L108" t="b">
         <v>1</v>
@@ -4768,31 +4780,31 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>10.63372044719365</v>
+        <v>10.98366496888179</v>
       </c>
       <c r="D109" t="n">
-        <v>4.570902978408131</v>
+        <v>4.324600896782196</v>
       </c>
       <c r="E109" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F109" t="n">
-        <v>15.02009350474195</v>
+        <v>14.65761334132564</v>
       </c>
       <c r="G109" t="n">
-        <v>3.658036321515232</v>
+        <v>3.461776251698633</v>
       </c>
       <c r="H109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I109" t="n">
         <v>111</v>
       </c>
       <c r="J109" t="n">
-        <v>0.009650320070671655</v>
+        <v>0.02625395852073091</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2895096021201496</v>
+        <v>0.7876187556219274</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4808,31 +4820,31 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.1789144770444</v>
+        <v>12.12844297996705</v>
       </c>
       <c r="D110" t="n">
-        <v>2.772815560150537</v>
+        <v>2.818718902673887</v>
       </c>
       <c r="E110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F110" t="n">
-        <v>17.88757932547056</v>
+        <v>17.79213748864986</v>
       </c>
       <c r="G110" t="n">
-        <v>2.013019523190567</v>
+        <v>2.037316279846102</v>
       </c>
       <c r="H110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I110" t="n">
         <v>19</v>
       </c>
       <c r="J110" t="n">
-        <v>7.590857348052369e-07</v>
+        <v>1.913423550711778e-06</v>
       </c>
       <c r="K110" t="n">
-        <v>2.277257204415711e-05</v>
+        <v>5.740270652135333e-05</v>
       </c>
       <c r="L110" t="b">
         <v>1</v>
@@ -4848,31 +4860,31 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>11.7441415924181</v>
+        <v>12.06953014159238</v>
       </c>
       <c r="D111" t="n">
-        <v>3.185789713190884</v>
+        <v>2.815173008719713</v>
       </c>
       <c r="E111" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F111" t="n">
-        <v>15.26591491769508</v>
+        <v>15.28413904219392</v>
       </c>
       <c r="G111" t="n">
-        <v>1.460749484119603</v>
+        <v>1.50383006127078</v>
       </c>
       <c r="H111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="J111" t="n">
-        <v>7.939058008787927e-05</v>
+        <v>0.0001469998802153171</v>
       </c>
       <c r="K111" t="n">
-        <v>0.002381717402636378</v>
+        <v>0.004409996406459514</v>
       </c>
       <c r="L111" t="b">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>10.03359667442254</v>
+        <v>9.945570330382292</v>
       </c>
       <c r="D112" t="n">
-        <v>2.53512727308281</v>
+        <v>2.549694221218427</v>
       </c>
       <c r="E112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F112" t="n">
-        <v>19.19224254482448</v>
+        <v>19.29428833139432</v>
       </c>
       <c r="G112" t="n">
-        <v>3.229911937984152</v>
+        <v>3.302623956661606</v>
       </c>
       <c r="H112" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I112" t="n">
         <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>1.13074397866807e-07</v>
+        <v>2.620605590347779e-07</v>
       </c>
       <c r="K112" t="n">
-        <v>3.392231936004209e-06</v>
+        <v>7.861816771043338e-06</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>8.982796436070581</v>
+        <v>8.980410684221461</v>
       </c>
       <c r="D113" t="n">
-        <v>2.837387928066507</v>
+        <v>2.895872359003035</v>
       </c>
       <c r="E113" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F113" t="n">
-        <v>13.9008372363189</v>
+        <v>13.65878834203501</v>
       </c>
       <c r="G113" t="n">
-        <v>2.012188989702753</v>
+        <v>1.818232856543573</v>
       </c>
       <c r="H113" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I113" t="n">
         <v>30</v>
       </c>
       <c r="J113" t="n">
-        <v>3.105300762762206e-06</v>
+        <v>8.246867290450602e-06</v>
       </c>
       <c r="K113" t="n">
-        <v>9.315902288286618e-05</v>
+        <v>0.000247406018713518</v>
       </c>
       <c r="L113" t="b">
         <v>1</v>
@@ -4968,31 +4980,31 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>15.57340122581006</v>
+        <v>15.82587561243209</v>
       </c>
       <c r="D114" t="n">
-        <v>2.87345803992248</v>
+        <v>2.647113507670345</v>
       </c>
       <c r="E114" t="n">
+        <v>24</v>
+      </c>
+      <c r="F114" t="n">
+        <v>20.04784215211959</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.8297730270237796</v>
+      </c>
+      <c r="H114" t="n">
+        <v>16</v>
+      </c>
+      <c r="I114" t="n">
         <v>25</v>
       </c>
-      <c r="F114" t="n">
-        <v>20.04853784087832</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0.8050028887545623</v>
-      </c>
-      <c r="H114" t="n">
-        <v>17</v>
-      </c>
-      <c r="I114" t="n">
-        <v>26</v>
-      </c>
       <c r="J114" t="n">
-        <v>1.877062189290695e-06</v>
+        <v>4.292096768385486e-06</v>
       </c>
       <c r="K114" t="n">
-        <v>5.631186567872086e-05</v>
+        <v>0.0001287629030515646</v>
       </c>
       <c r="L114" t="b">
         <v>1</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.04042704727311</v>
+        <v>12.07792850150386</v>
       </c>
       <c r="D115" t="n">
-        <v>2.945209326520859</v>
+        <v>3.000087734716991</v>
       </c>
       <c r="E115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F115" t="n">
-        <v>16.63864289600971</v>
+        <v>16.58618551728046</v>
       </c>
       <c r="G115" t="n">
-        <v>2.032602279853325</v>
+        <v>2.083964689697389</v>
       </c>
       <c r="H115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I115" t="n">
         <v>49</v>
       </c>
       <c r="J115" t="n">
-        <v>2.955656090988942e-05</v>
+        <v>8.350097704504365e-05</v>
       </c>
       <c r="K115" t="n">
-        <v>0.0008866968272966825</v>
+        <v>0.00250502931135131</v>
       </c>
       <c r="L115" t="b">
         <v>1</v>
@@ -5048,31 +5060,31 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>14.1482211565745</v>
+        <v>14.23953137118585</v>
       </c>
       <c r="D116" t="n">
-        <v>1.838402934361745</v>
+        <v>1.819919876342134</v>
       </c>
       <c r="E116" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F116" t="n">
-        <v>19.74328358208951</v>
+        <v>19.70773163058279</v>
       </c>
       <c r="G116" t="n">
-        <v>1.694562923111058</v>
+        <v>1.740553925566712</v>
       </c>
       <c r="H116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K116" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L116" t="b">
         <v>1</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>8.607058623233625</v>
+        <v>8.823025556627494</v>
       </c>
       <c r="D117" t="n">
-        <v>3.547822015107442</v>
+        <v>3.456220216751092</v>
       </c>
       <c r="E117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F117" t="n">
-        <v>18.96007854932445</v>
+        <v>18.93455757689684</v>
       </c>
       <c r="G117" t="n">
-        <v>2.551701673329235</v>
+        <v>2.628128198633697</v>
       </c>
       <c r="H117" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I117" t="n">
         <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>7.398027950986396e-08</v>
+        <v>1.679640427507783e-07</v>
       </c>
       <c r="K117" t="n">
-        <v>2.219408385295919e-06</v>
+        <v>5.03892128252335e-06</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,31 +5140,31 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>10.86287958752954</v>
+        <v>10.92654717724988</v>
       </c>
       <c r="D118" t="n">
-        <v>2.769846154510771</v>
+        <v>2.808981545885253</v>
       </c>
       <c r="E118" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F118" t="n">
-        <v>16.32245390911216</v>
+        <v>15.98993664924429</v>
       </c>
       <c r="G118" t="n">
-        <v>4.017810080277761</v>
+        <v>3.9079497602176</v>
       </c>
       <c r="H118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I118" t="n">
         <v>74</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0004058747458892882</v>
+        <v>0.00117894338145478</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01217624237667865</v>
+        <v>0.03536830144364341</v>
       </c>
       <c r="L118" t="b">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>9.605993229365831</v>
+        <v>9.683943941604438</v>
       </c>
       <c r="D119" t="n">
-        <v>2.517166664100954</v>
+        <v>2.539335643500289</v>
       </c>
       <c r="E119" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F119" t="n">
-        <v>21.41060796561851</v>
+        <v>21.46237659173636</v>
       </c>
       <c r="G119" t="n">
-        <v>1.579329198889496</v>
+        <v>1.61388147715896</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>5.557752873173323e-08</v>
+        <v>1.244002736502803e-07</v>
       </c>
       <c r="K119" t="n">
-        <v>1.667325861951997e-06</v>
+        <v>3.73200820950841e-06</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,31 +5220,31 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>12.04156869077463</v>
+        <v>11.80698664287027</v>
       </c>
       <c r="D120" t="n">
-        <v>4.755638768989456</v>
+        <v>4.709853413361566</v>
       </c>
       <c r="E120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F120" t="n">
-        <v>16.19504375582718</v>
+        <v>15.70432566325297</v>
       </c>
       <c r="G120" t="n">
-        <v>4.707943860776179</v>
+        <v>4.410936314438173</v>
       </c>
       <c r="H120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I120" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="J120" t="n">
-        <v>0.02939745744471163</v>
+        <v>0.03468619745527803</v>
       </c>
       <c r="K120" t="n">
-        <v>0.8819237233413491</v>
+        <v>1</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5248,31 +5260,31 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>13.65531953710389</v>
+        <v>13.83634860267138</v>
       </c>
       <c r="D121" t="n">
-        <v>2.606565068993272</v>
+        <v>2.501596348036692</v>
       </c>
       <c r="E121" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F121" t="n">
-        <v>17.55936511348682</v>
+        <v>17.59089850776919</v>
       </c>
       <c r="G121" t="n">
-        <v>1.683890979237074</v>
+        <v>1.730838769959177</v>
       </c>
       <c r="H121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I121" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J121" t="n">
-        <v>1.670002705729528e-05</v>
+        <v>3.669225248162476e-05</v>
       </c>
       <c r="K121" t="n">
-        <v>0.0005010008117188584</v>
+        <v>0.001100767574448743</v>
       </c>
       <c r="L121" t="b">
         <v>1</v>
